--- a/data/intermediate/Aor_reduced_metabolite_table.xlsx
+++ b/data/intermediate/Aor_reduced_metabolite_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="1562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="1566">
   <si>
     <t xml:space="preserve">NAME</t>
   </si>
@@ -1286,1965 +1286,1971 @@
     <t xml:space="preserve">2-deoxy-D-ribose 5-phosphate</t>
   </si>
   <si>
+    <t xml:space="preserve">DEORIPI[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-deoxy-D-gluconic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEXG[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">digalactosyl diglyceride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGDG[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dGDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGDP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-glucose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGLC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dGMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGMP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diacylglycerol pyrophosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGPP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dGTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGTP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dihydrodemethylsterigmatocystin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHDMST[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dihydrofolate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHF[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dihydro-O-methylsterigmatocystin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHOMST[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,8-dihydroneopterin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-dehydroshikimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHSK[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sphinganine 1-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHSP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-dehydrosphinganine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C18DHSPH[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dihydrosterigmatocystin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHST[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(S)-2,3-dihydrodipicolinate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIDIPC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,3-dihydroxyindole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIHINDOLE[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,6-dihydrouracil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIHURA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N,N-dimethylglycine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIMEGLY[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dimethylallyl diphosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMPP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6-demethylsterigmatocystin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMST[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14-demethyllanosterol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCDOL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deoxyribonucleic acids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-dopa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDOPA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-dopaquinone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOQUI[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(S)-dihydroorotate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOROA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dephospho-CoA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPCOA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-proline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPRO[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-dehydroquinate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DQT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-deoxyribose 1-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR1P[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thymidine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dethiobiotin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DTB[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dTTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DTTP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deoxyuridine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DU[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dUMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUMP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-erythrose 4-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4P[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">erythritol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EOL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">episterol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPST[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sterol ester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERGOSE[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ergosterol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERGOST[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eriodictyol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERIDICOL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,7,22,24(28)-ergostatetraenol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERGOT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,7,24(28)-ergostatrienol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERTROL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ethanol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETH[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta-D-fructofuranose 6-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F6P[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAD[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">formaldehyde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FALD[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta-D-fructofuranose 1,6-bisphosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ferreirin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERRIN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fecosterol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEST[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">free fatty acids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-formylkynurenine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FKYN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FMN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FMN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">formate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOR[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-formimidoyl-L-glutamate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORGLU[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">formamide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-trans,6-trans-farnesyl diphosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FPP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-fructose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRU[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-fructuronate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUTN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-formyltetrahydrofolate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTHF[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fumarate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUM[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-glycerate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alpha-D-glucose 1-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G1P[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alpha-D-glucose 6-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G6P[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-glucosamine 6-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GA6P[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gamma-aminobutyrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-aminobutanal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABAL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">galactocyl ceremide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GACER[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-galactono-1,4-lactone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GALN14LAC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-galactonate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GALNT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">galactitol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GALOL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-galacturonate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GALUNT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDP-mannose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDPMAN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geranylgeranyl diphosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GGPP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glycerol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sn-glycerol 3-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL3P[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-galactose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLAC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glycoaldehyde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLAL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alpha-D-glucose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-glucosamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLCN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-glucono-1,5-lactone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLCN15LAC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-gluconate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLCNT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-glutamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-glutamate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLU[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(S)-4-amino-5-oxopentanoic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLU1SAL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-glucuronate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLCUNT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta-D-glucosiduronic acids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLUCRE[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-glutamate 5-semialdehyde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLUGSAL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-alpha-glutamyl phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLUP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glyoxylate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLX[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glycine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLY[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-glyceraldehyde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLYAL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glycine betaine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLYBET[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glycerophosphocholine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLYCEROCHO[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glycogen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLYCO[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glycerone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLYN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">guanine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geranyl diphosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GTP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydrogen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H(+) (energy metabolism)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H_PO[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2O[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydrogen peroxide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2O2[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2O2[p]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2S[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sulfite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2SO3[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(S)-3-hydroxy-3-methylglutaryl-CoA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H3MCOA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">but-1-ene-1,2,4-tricarboxylate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HACN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-hydroxyaverantin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAVN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">homocitrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCIT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCO3[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-homocysteine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCYS[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-histidine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIS[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-histidinol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HISOL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-histidinol phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HISOLP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-hydroxyisourate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIUR[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-hydroxykynurenine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HKYN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydroxymethylbilane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HMBIL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nitrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNO2[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nitrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNO3[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">homogentisate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOMOGEN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trans-4-hydroxy-L-proline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPRO[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-homoserine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSER[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HX[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-(hydroxymethyl)glutathione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYGTA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">indole-3-acetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INAC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">indole-3-acetamide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAD[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isocitrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICIT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,4-dimethylcholesta-8,14,24-trienol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCTOL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intermediate methylzymosterol II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IIMZYMST[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intermediate zymosterol II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IIZYMST[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-isoleucine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILE[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-(imidazol-4-yl)-2-oxopropyl phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMACP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(S)-3-(5-oxo-4,5-dihydro-3H-imidazol-4-yl)propanoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMIPRO[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intermediate methylzymosterol I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMZYMST[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inosine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inositol phosphorylceramide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isopenicillin N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-isopropylmalate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2IPPMAL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isopentenyl diphosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPPP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">itaconate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intermediate zymosterol I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IZYMST[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">potassium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-kynurenine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KYN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(R)-lactate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(R)-lactaldehyde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LACAL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lactose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LACT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-arabinitol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAOL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-arabinose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LARAB[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-leucine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEU[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-galactonate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LGALNT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-glutamyl-tRNA(Glu)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AATRNA_GLU[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-glyceraldehyde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LGLYAL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(R)-S-lactoylglutathione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LGT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(S)-lactate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLAC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-cystathionine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLCT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-[L-5-amino-5-carboxypentanoyl]-L-cysteinyl-D-valine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLDACV[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-methionyl-tRNA(Met)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AATRNA_MET[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lysophosphatidylamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPAA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lysophosphatidylcholine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lysophosphatidyl-N-dimethylethanolamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPDME[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-lysophosphatidylethanolamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPE[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lysophosphatidylglycerol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPG[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lysophosphatidyl-N-methylethanolamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPMME[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-prolyl-tRNA(Pro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AATRNA_PRO[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lysophosphatidylserine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPS[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-ribulose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LRL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-ribulose 5-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LRL5P[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-selenocysteinyl-tRNA(Sec)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSECTRNA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-seryl-tRNA(Ser)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AATRNA_SER[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5alpha-cholest-7-en-3beta-ol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LTST[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-tyrosyl-tRNA(Tyr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AATRNA_TYR[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-xylulose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LXUL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-lysine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LYS[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-monoglycerides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAGLY[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(S)-malate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">malonyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALACP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">malonyl-CoA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALCOA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-mannose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-mannose 6-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN6P[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mannans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANNAN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-mannonate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMANA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-methylacetoacetyl-CoA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2MAACCOA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melibiose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MELI[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melanins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MENIN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mesaconate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MESC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-methionine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MET[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-methyl-2-hydroxybutyryl-CoA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METBYCOA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,10-methenyltetrahydrofolate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METHF[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">methanol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METHOL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,10-methylenetetrahydrofolate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METTHF[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,2-diacyl-3-beta-D-galactosyl-sn-glycerol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGDG[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N(pi)-methyl-L-histidine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MHIS[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1D-myo-inositol 3-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI1P[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inositol-mannose-P-inositol-P-D-ceramide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIP2C[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mannose-inositol-P-ceramide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIPC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maltose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maltotriose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLTRIO[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(S)-methylmalonyl-CoA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMCOA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-mannitol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-mannitol 1-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNT1P[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-methyltetrahydrofolate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTHF[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">methylglyoxal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTHGXL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-methyltetrahydropteroyltri-L-glutamate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTHPTGLU[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(R)-mevalonate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1D-myo-inositol 1,4-bisphosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYOBISPI[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1D-myo-inositol 1,2-cyclic phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYOCYPI[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">myo-inositol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYOI[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4alpha-methylzymosterol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MZYMST[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sodium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAD(+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAD[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADH[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADPH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADPH[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-acetyl-D-glucosamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAG[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-acetyl-D-glucosamine 6-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAGA6P[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N2-acetyl-L-ornithine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAORN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2',4,4',6'-tetrahydroxychalcone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCACE[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">naringenin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NARINGE[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NH3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NH3[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ammonium hydroxide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NH4OH[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nicotinamide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NICD[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nicotinate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NICA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nitrile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NITE[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-nitropropane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NITROPRO[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oxidonitrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">norsolorinic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOR[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oxygen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O2[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oxaloacetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O-acetyl-L-homoserine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OAHSER[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-oxobutanoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBUT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oxidized glutathione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OGT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2S)-2-isopropyl-3-oxosuccinate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OICAP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(R)-3-methyl-2-oxobutanoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OIVAL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orotidine 5'-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-O-methylsterigmatocystin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMST[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-keto-3-methyl-valerate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMVAL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-ornithine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orotate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OROA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O-succinyl-L-homoserine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSLHSER[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oxalate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OXAL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-hydroxy-3-oxosuccinic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OXGLY[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(S)-1-pyrroline-5-carboxylate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P5C[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatidate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLPA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatidylamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-aminobenzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PABA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-phenylacetamide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAD[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(R)-pantoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adenosine 3',5'-bisphosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatidylcholines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,4-dihydroxybenzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choline phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCHO[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatidyl-N-dimethylethanolamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCPDME[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pyridoxal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pyridoxamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDXAM[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pyridoxamine 5'-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDXAM5PI[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pyridoxine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDXI[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pyridoxine 5'-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDXI5PI[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pyridoxal 5'-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatidylethanolamines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCPE[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penicillins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penicillanic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENACID[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penicillin G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENG[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penicillin N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphoenolpyruvate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ethanolamine phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PETHM[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatidylglycerol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phenylacetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHAC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phenylacetaldehyde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHAL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phenylacetyl-CoA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHACCOA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-1-pyrroline-3-hydroxy-5-carboxylate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-phenylalanine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHE[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-phenylethanol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHEETHAL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-phosphonooxypyruvate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">keto-phenylpyruvate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHPYR[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O-phospho-L-homoserine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHSER[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytosphingosine 1-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHSP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PI[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-phosphatidyl-1D-myo-inositols</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINS[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-phosphatidyl-1D-myo-inositol 4-phosphates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINS4P[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-phosphatidyl-1D-myo-inositol 3-phosphates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINSP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatidyl-N-methylethanolamines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCPMME[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">porphobilinogen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORBILEN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protoporphyrinogen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROPHYR[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">guanosine 3',5'-bis(diphosphate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ppGpp[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diphosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPI[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">guanosine 3'-diphosphate 5'-triphosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pppGpp[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-proline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRO[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">propionate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">propionyl-CoA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROPCOA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protein[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein for biomass and amylase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protein_Amylase[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-phospho-alpha-D-ribose 1-diphosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRPP[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatidylserine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytosphingosine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C18PSPH[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">putrescine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUTR[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pseudouridine 5'-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PURI5P[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pyruvate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PYR[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">myo-inositol hexakisphosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHYA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quinolinate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUIN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-ribose 1-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R1P[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-ribose 5-phosphate</t>
+  </si>
+  <si>
     <t xml:space="preserve">R5P[c]</t>
   </si>
   <si>
-    <t xml:space="preserve">2-deoxy-D-gluconic acid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEXG[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">digalactosyl diglyceride</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGDG[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dGDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGDP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-glucose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGLC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dGMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGMP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diacylglycerol pyrophosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGPP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dGTP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGTP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dihydrodemethylsterigmatocystin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHDMST[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dihydrofolate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHF[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dihydro-O-methylsterigmatocystin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHOMST[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,8-dihydroneopterin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-dehydroshikimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHSK[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sphinganine 1-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHSP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-dehydrosphinganine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C18DHSPH[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dihydrosterigmatocystin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHST[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(S)-2,3-dihydrodipicolinate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIDIPC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,3-dihydroxyindole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIHINDOLE[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,6-dihydrouracil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIHURA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N,N-dimethylglycine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIMEGLY[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dimethylallyl diphosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMPP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6-demethylsterigmatocystin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMST[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14-demethyllanosterol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCDOL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deoxyribonucleic acids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-dopa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LDOPA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-dopaquinone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOQUI[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(S)-dihydroorotate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOROA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dephospho-CoA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DPCOA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-proline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DPRO[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-dehydroquinate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DQT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-deoxyribose 1-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR1P[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">thymidine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dethiobiotin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DTB[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dTTP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DTTP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deoxyuridine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DU[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dUMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUMP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-erythrose 4-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E4P[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">erythritol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EOL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">episterol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPST[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sterol ester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERGOSE[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ergosterol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERGOST[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eriodictyol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERIDICOL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,7,22,24(28)-ergostatetraenol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERGOT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,7,24(28)-ergostatrienol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERTROL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ethanol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETH[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beta-D-fructofuranose 6-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F6P[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAD[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">formaldehyde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FALD[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beta-D-fructofuranose 1,6-bisphosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FDP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ferreirin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FERRIN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fecosterol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEST[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">free fatty acids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-formylkynurenine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FKYN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FMN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FMN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">formate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOR[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-formimidoyl-L-glutamate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FORGLU[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">formamide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-trans,6-trans-farnesyl diphosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FPP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-fructose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRU[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-fructuronate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRUTN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-formyltetrahydrofolate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTHF[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fumarate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUM[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-glycerate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">alpha-D-glucose 1-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G1P[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">alpha-D-glucose 6-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G6P[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-glucosamine 6-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GA6P[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gamma-aminobutyrate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GABA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4-aminobutanal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GABAL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">galactocyl ceremide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GACER[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-galactono-1,4-lactone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GALN14LAC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-galactonate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GALNT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">galactitol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GALOL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-galacturonate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GALUNT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDP-mannose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDPMAN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geranylgeranyl diphosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GGPP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glycerol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sn-glycerol 3-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GL3P[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-galactose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLAC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glycoaldehyde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLAL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">alpha-D-glucose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-glucosamine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLCN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-glucono-1,5-lactone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLCN15LAC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-gluconate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLCNT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-glutamine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-glutamate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLU[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(S)-4-amino-5-oxopentanoic acid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLU1SAL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-glucuronate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLCUNT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beta-D-glucosiduronic acids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLUCRE[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-glutamate 5-semialdehyde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLUGSAL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-alpha-glutamyl phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLUP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glyoxylate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLX[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glycine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLY[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-glyceraldehyde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLYAL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glycine betaine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLYBET[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glycerophosphocholine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLYCEROCHO[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glycogen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLYCO[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glycerone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLYN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GMP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">guanine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geranyl diphosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GTP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GTP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hydrogen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H(+) (energy metabolism)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H_PO[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2O[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hydrogen peroxide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2O2[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2O2[p]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2S[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sulfite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2SO3[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(S)-3-hydroxy-3-methylglutaryl-CoA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H3MCOA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">but-1-ene-1,2,4-tricarboxylate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HACN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-hydroxyaverantin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAVN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">homocitrate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCIT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCO3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCO3[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-homocysteine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCYS[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-histidine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIS[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-histidinol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HISOL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-histidinol phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HISOLP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-hydroxyisourate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIUR[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-hydroxykynurenine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HKYN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hydroxymethylbilane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HMBIL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nitrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNO2[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nitrate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNO3[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">homogentisate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOMOGEN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trans-4-hydroxy-L-proline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPRO[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-homoserine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSER[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HX[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-(hydroxymethyl)glutathione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYGTA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">indole-3-acetate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INAC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">indole-3-acetamide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAD[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">isocitrate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICIT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,4-dimethylcholesta-8,14,24-trienol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCTOL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intermediate methylzymosterol II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IIMZYMST[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intermediate zymosterol II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IIZYMST[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-isoleucine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILE[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-(imidazol-4-yl)-2-oxopropyl phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMACP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(S)-3-(5-oxo-4,5-dihydro-3H-imidazol-4-yl)propanoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMIPRO[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intermediate methylzymosterol I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMZYMST[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inosine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INS[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inositol phosphorylceramide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">isopenicillin N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-isopropylmalate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2IPPMAL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">isopentenyl diphosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPPP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">itaconate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intermediate zymosterol I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IZYMST[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">potassium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-kynurenine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KYN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(R)-lactate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(R)-lactaldehyde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LACAL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lactose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LACT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-arabinitol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAOL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-arabinose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LARAB[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-leucine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEU[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-galactonate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LGALNT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-glutamyl-tRNA(Glu)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AATRNA_GLU[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-glyceraldehyde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LGLYAL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(R)-S-lactoylglutathione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LGT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(S)-lactate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LLAC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-cystathionine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LLCT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-[L-5-amino-5-carboxypentanoyl]-L-cysteinyl-D-valine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LLDACV[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-methionyl-tRNA(Met)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AATRNA_MET[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lysophosphatidylamine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPAA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lysophosphatidylcholine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lysophosphatidyl-N-dimethylethanolamine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPDME[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-lysophosphatidylethanolamine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPE[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lysophosphatidylglycerol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPG[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lysophosphatidyl-N-methylethanolamine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPMME[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-prolyl-tRNA(Pro)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AATRNA_PRO[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lysophosphatidylserine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPS[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-ribulose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LRL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-ribulose 5-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LRL5P[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-selenocysteinyl-tRNA(Sec)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LSECTRNA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-seryl-tRNA(Ser)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AATRNA_SER[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5alpha-cholest-7-en-3beta-ol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LTST[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-tyrosyl-tRNA(Tyr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AATRNA_TYR[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-xylulose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LXUL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-lysine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LYS[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-monoglycerides</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAGLY[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(S)-malate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">malonyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MALACP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">malonyl-CoA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MALCOA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-mannose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-mannose 6-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN6P[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mannans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANNAN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-mannonate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMANA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-methylacetoacetyl-CoA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2MAACCOA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melibiose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MELI[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melanins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MENIN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mesaconate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MESC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-methionine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MET[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-methyl-2-hydroxybutyryl-CoA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METBYCOA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,10-methenyltetrahydrofolate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METHF[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">methanol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METHOL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,10-methylenetetrahydrofolate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METTHF[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,2-diacyl-3-beta-D-galactosyl-sn-glycerol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGDG[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N(pi)-methyl-L-histidine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MHIS[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1D-myo-inositol 3-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI1P[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inositol-mannose-P-inositol-P-D-ceramide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIP2C[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mannose-inositol-P-ceramide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIPC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maltose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maltotriose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLTRIO[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(S)-methylmalonyl-CoA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMCOA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-mannitol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MNT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-mannitol 1-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MNT1P[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-methyltetrahydrofolate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTHF[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">methylglyoxal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTHGXL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-methyltetrahydropteroyltri-L-glutamate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTHPTGLU[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(R)-mevalonate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MVL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1D-myo-inositol 1,4-bisphosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYOBISPI[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1D-myo-inositol 1,2-cyclic phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYOCYPI[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">myo-inositol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYOI[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4alpha-methylzymosterol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MZYMST[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sodium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Na[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAD(+)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAD[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADH[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADPH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADPH[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-acetyl-D-glucosamine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAG[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-acetyl-D-glucosamine 6-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAGA6P[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N2-acetyl-L-ornithine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAORN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2',4,4',6'-tetrahydroxychalcone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCACE[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">naringenin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NARINGE[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NH3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NH3[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ammonium hydroxide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NH4OH[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nicotinamide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NICD[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nicotinate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NICA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nitrile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NITE[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-nitropropane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NITROPRO[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oxidonitrate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">norsolorinic acid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOR[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oxygen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O2[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oxaloacetate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O-acetyl-L-homoserine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OAHSER[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-oxobutanoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBUT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oxidized glutathione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OGT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2S)-2-isopropyl-3-oxosuccinate</t>
+    <t xml:space="preserve">glutathione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RGT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-ribose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIB[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">riboflavin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBOFLAV[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-ribulose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RL[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ribonucleic acids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RNA[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sulfur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-adenosyl-L-homocysteine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAH[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2S)-2-[5-amino-1-(5-phospho-beta-D-ribosyl)imidazole-4-carboxamido]succinic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAICAR[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-adenosyl-L-methionine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAM[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sarcosine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SARC[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scytalone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCTLE[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-serine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SER[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sulfate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLF[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selenophosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNPI[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-sorbose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOR[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-sorbitol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOT[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sphinganine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C18SPH[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ceramide phosphocholines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPMYLIN[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spermidine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPERM[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sterigmatocystin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">starch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STARCH[c]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">succinate</t>
   </si>
   <si>
     <t xml:space="preserve">SUCC[c]</t>
   </si>
   <si>
-    <t xml:space="preserve">(R)-3-methyl-2-oxobutanoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OIVAL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orotidine 5'-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OMP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7-O-methylsterigmatocystin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OMST[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-keto-3-methyl-valerate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OMVAL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-ornithine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orotate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OROA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O-succinyl-L-homoserine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSLHSER[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oxalate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OXAL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-hydroxy-3-oxosuccinic acid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OXGLY[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(S)-1-pyrroline-5-carboxylate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P5C[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phosphatidate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLPA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phosphatidylamine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4-aminobenzoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PABA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-phenylacetamide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAD[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(R)-pantoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PANT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adenosine 3',5'-bisphosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phosphatidylcholines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,4-dihydroxybenzoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">choline phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCHO[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phosphatidyl-N-dimethylethanolamine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCPDME[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pyridoxal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pyridoxamine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDXAM[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pyridoxamine 5'-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDXAM5PI[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pyridoxine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDXI[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pyridoxine 5'-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDXI5PI[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pyridoxal 5'-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phosphatidylethanolamines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCPE[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penicillins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penicillanic acid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENACID[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penicillin G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENG[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penicillin N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phosphoenolpyruvate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ethanolamine phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PETHM[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phosphatidylglycerol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PG[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phenylacetate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHAC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phenylacetaldehyde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHAL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phenylacetyl-CoA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHACCOA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-1-pyrroline-3-hydroxy-5-carboxylate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-phenylalanine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHE[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-phenylethanol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHEETHAL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-phosphonooxypyruvate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">keto-phenylpyruvate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHPYR[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O-phospho-L-homoserine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHSER[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytosphingosine 1-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHSP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PI[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-phosphatidyl-1D-myo-inositols</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINS[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-phosphatidyl-1D-myo-inositol 4-phosphates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINS4P[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-phosphatidyl-1D-myo-inositol 3-phosphates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINSP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phosphatidyl-N-methylethanolamines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCPMME[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">porphobilinogen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORBILEN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">protoporphyrinogen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROPHYR[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">guanosine 3',5'-bis(diphosphate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ppGpp[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diphosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPI[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">guanosine 3'-diphosphate 5'-triphosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pppGpp[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-proline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRO[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">propionate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">propionyl-CoA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROPCOA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">protein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protein[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">protein for biomass and amylase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protein_Amylase[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-phospho-alpha-D-ribose 1-diphosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRPP[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phosphatidylserine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytosphingosine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C18PSPH[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">putrescine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUTR[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pseudouridine 5'-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PURI5P[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pyruvate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PYR[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">myo-inositol hexakisphosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHYA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">quinolinate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QUIN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-ribose 1-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R1P[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-ribose 5-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glutathione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RGT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-ribose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RIB[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">riboflavin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RIBOFLAV[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-ribulose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RL[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ribonucleic acids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNA[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sulfur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-adenosyl-L-homocysteine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAH[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2S)-2-[5-amino-1-(5-phospho-beta-D-ribosyl)imidazole-4-carboxamido]succinic acid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAICAR[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-adenosyl-L-methionine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAM[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sarcosine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SARC[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scytalone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCTLE[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-serine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SER[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sulfate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLF[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">selenophosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNPI[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-sorbose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOR[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-sorbitol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOT[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sphinganine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C18SPH[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ceramide phosphocholines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPMYLIN[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spermidine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPERM[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sterigmatocystin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ST[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">starch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STARCH[c]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">succinate</t>
-  </si>
-  <si>
     <t xml:space="preserve">succinate semialdehyde</t>
   </si>
   <si>
@@ -4262,240 +4268,243 @@
     <t xml:space="preserve">DIMEGLY[m]</t>
   </si>
   <si>
+    <t xml:space="preserve">DOROA[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETH[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FADH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FADH2[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAD[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FALD[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ferricytochrome c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERI[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ferrocytochrome c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERO[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FMN[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-formylmethionyl-tRNA(fMet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOFMET[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOR[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTHF[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUM[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL3P[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLN[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLUGSAL[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLU[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLX[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLY[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H(+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H_PO[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2O2[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2O[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H3MCOA[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCO3[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heme a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEME_A[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heme o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEME_O[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HKYN[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPRO[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-hydroxy-2-methylpropanoyl-CoA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYISOCOA[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICIT[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILE[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2IPPMAL[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KYN[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEU[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-glutaminyl-tRNA(Gln)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AATRNA_GLN[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AATRNA_MET[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-threonyl-tRNA(Thr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AATRNA_THR[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAL[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-methylbut-2-enoyl-CoA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2MC41COA[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METHF[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METTHF[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTHF[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTHGXL[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADH[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAD[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADPH[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADP[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-acetyl-L-glutamate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAGLU[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-acetyl-L-gamma-glutamyl phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAGLUP[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-acetyl-L-glutamate 5-semialdehyde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAGLUS[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NH3[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NICD[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NICA[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nicotinamide mononucleotide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NMN[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O2[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OA[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OICAP[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OIVAL[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMVAL[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORN[m]</t>
+  </si>
+  <si>
     <t xml:space="preserve">OROA[m]</t>
   </si>
   <si>
-    <t xml:space="preserve">ETH[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FADH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FADH2[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAD[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FALD[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ferricytochrome c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FERI[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ferrocytochrome c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FERO[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FMN[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-formylmethionyl-tRNA(fMet)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOFMET[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOR[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTHF[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUM[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GL3P[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLN[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLUGSAL[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLU[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLX[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLY[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H(+)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H_PO[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2O2[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2O[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H3MCOA[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCO3[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">heme a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEME_A[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">heme o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEME_O[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HKYN[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPRO[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-hydroxy-2-methylpropanoyl-CoA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYISOCOA[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICIT[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILE[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2IPPMAL[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KYN[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEU[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-glutaminyl-tRNA(Gln)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AATRNA_GLN[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AATRNA_MET[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-threonyl-tRNA(Thr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AATRNA_THR[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAL[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-methylbut-2-enoyl-CoA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2MC41COA[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METHF[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METTHF[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTHF[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTHGXL[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADH[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAD[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADPH[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADP[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-acetyl-L-glutamate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAGLU[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-acetyl-L-gamma-glutamyl phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAGLUP[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-acetyl-L-glutamate 5-semialdehyde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAGLUS[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Na[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NH3[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NICD[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NICA[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nicotinamide mononucleotide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NMN[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O2[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OA[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OICAP[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OIVAL[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OMVAL[m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORN[m]</t>
-  </si>
-  <si>
     <t xml:space="preserve">P5C[m]</t>
   </si>
   <si>
@@ -4668,6 +4677,9 @@
   </si>
   <si>
     <t xml:space="preserve">SUCC[p]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UGC[p]</t>
   </si>
   <si>
     <t xml:space="preserve">UREA[p]</t>
@@ -10699,942 +10711,942 @@
         <v>4</v>
       </c>
       <c r="C516" t="s">
-        <v>424</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B517" t="s">
         <v>4</v>
       </c>
       <c r="C517" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B518" t="s">
         <v>4</v>
       </c>
       <c r="C518" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B519" t="s">
         <v>4</v>
       </c>
       <c r="C519" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B520" t="s">
         <v>4</v>
       </c>
       <c r="C520" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B521" t="s">
         <v>4</v>
       </c>
       <c r="C521" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B522" t="s">
         <v>4</v>
       </c>
       <c r="C522" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B523" t="s">
         <v>4</v>
       </c>
       <c r="C523" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B524" t="s">
         <v>4</v>
       </c>
       <c r="C524" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B525" t="s">
         <v>4</v>
       </c>
       <c r="C525" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B526" t="s">
         <v>4</v>
       </c>
       <c r="C526" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B527" t="s">
         <v>4</v>
       </c>
       <c r="C527" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B528" t="s">
         <v>4</v>
       </c>
       <c r="C528" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B529" t="s">
         <v>4</v>
       </c>
       <c r="C529" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B530" t="s">
         <v>4</v>
       </c>
       <c r="C530" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B531" t="s">
         <v>4</v>
       </c>
       <c r="C531" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B532" t="s">
         <v>4</v>
       </c>
       <c r="C532" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B533" t="s">
         <v>4</v>
       </c>
       <c r="C533" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B534" t="s">
         <v>4</v>
       </c>
       <c r="C534" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B535" t="s">
         <v>4</v>
       </c>
       <c r="C535" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B536" t="s">
         <v>4</v>
       </c>
       <c r="C536" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B537" t="s">
         <v>4</v>
       </c>
       <c r="C537" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B538" t="s">
         <v>4</v>
       </c>
       <c r="C538" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B539" t="s">
         <v>4</v>
       </c>
       <c r="C539" t="s">
-        <v>894</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="B540" t="s">
         <v>4</v>
       </c>
       <c r="C540" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="B541" t="s">
         <v>4</v>
       </c>
       <c r="C541" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="B542" t="s">
         <v>4</v>
       </c>
       <c r="C542" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="B543" t="s">
         <v>4</v>
       </c>
       <c r="C543" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B544" t="s">
         <v>4</v>
       </c>
       <c r="C544" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="B545" t="s">
         <v>4</v>
       </c>
       <c r="C545" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="B546" t="s">
         <v>4</v>
       </c>
       <c r="C546" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B547" t="s">
         <v>4</v>
       </c>
       <c r="C547" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="B548" t="s">
         <v>4</v>
       </c>
       <c r="C548" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="B549" t="s">
         <v>4</v>
       </c>
       <c r="C549" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="B550" t="s">
         <v>4</v>
       </c>
       <c r="C550" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="B551" t="s">
         <v>4</v>
       </c>
       <c r="C551" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B552" t="s">
         <v>4</v>
       </c>
       <c r="C552" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B553" t="s">
         <v>4</v>
       </c>
       <c r="C553" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="B554" t="s">
         <v>4</v>
       </c>
       <c r="C554" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B555" t="s">
         <v>4</v>
       </c>
       <c r="C555" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B556" t="s">
         <v>4</v>
       </c>
       <c r="C556" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="B557" t="s">
         <v>4</v>
       </c>
       <c r="C557" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="B558" t="s">
         <v>4</v>
       </c>
       <c r="C558" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="B559" t="s">
         <v>4</v>
       </c>
       <c r="C559" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="B560" t="s">
         <v>4</v>
       </c>
       <c r="C560" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B561" t="s">
         <v>4</v>
       </c>
       <c r="C561" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="B562" t="s">
         <v>4</v>
       </c>
       <c r="C562" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="B563" t="s">
         <v>4</v>
       </c>
       <c r="C563" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="B564" t="s">
         <v>4</v>
       </c>
       <c r="C564" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B565" t="s">
         <v>4</v>
       </c>
       <c r="C565" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="B566" t="s">
         <v>4</v>
       </c>
       <c r="C566" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="B567" t="s">
         <v>4</v>
       </c>
       <c r="C567" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="B568" t="s">
         <v>4</v>
       </c>
       <c r="C568" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="B569" t="s">
         <v>4</v>
       </c>
       <c r="C569" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="B570" t="s">
         <v>4</v>
       </c>
       <c r="C570" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="B571" t="s">
         <v>4</v>
       </c>
       <c r="C571" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B572" t="s">
         <v>4</v>
       </c>
       <c r="C572" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="B573" t="s">
         <v>4</v>
       </c>
       <c r="C573" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="B574" t="s">
         <v>4</v>
       </c>
       <c r="C574" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="B575" t="s">
         <v>4</v>
       </c>
       <c r="C575" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B576" t="s">
         <v>4</v>
       </c>
       <c r="C576" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="B577" t="s">
         <v>4</v>
       </c>
       <c r="C577" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="B578" t="s">
         <v>4</v>
       </c>
       <c r="C578" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="B579" t="s">
         <v>4</v>
       </c>
       <c r="C579" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="B580" t="s">
         <v>4</v>
       </c>
       <c r="C580" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="B581" t="s">
         <v>4</v>
       </c>
       <c r="C581" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B582" t="s">
         <v>4</v>
       </c>
       <c r="C582" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="B583" t="s">
         <v>4</v>
       </c>
       <c r="C583" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="B584" t="s">
         <v>4</v>
       </c>
       <c r="C584" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="B585" t="s">
         <v>4</v>
       </c>
       <c r="C585" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="B586" t="s">
         <v>4</v>
       </c>
       <c r="C586" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="B587" t="s">
         <v>4</v>
       </c>
       <c r="C587" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="B588" t="s">
         <v>4</v>
       </c>
       <c r="C588" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="B589" t="s">
         <v>4</v>
       </c>
       <c r="C589" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="B590" t="s">
         <v>4</v>
       </c>
       <c r="C590" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="B591" t="s">
         <v>4</v>
       </c>
       <c r="C591" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="B592" t="s">
         <v>4</v>
       </c>
       <c r="C592" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="B593" t="s">
         <v>4</v>
       </c>
       <c r="C593" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="B594" t="s">
         <v>4</v>
       </c>
       <c r="C594" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="B595" t="s">
         <v>4</v>
       </c>
       <c r="C595" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="B596" t="s">
         <v>4</v>
       </c>
       <c r="C596" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="B597" t="s">
         <v>4</v>
       </c>
       <c r="C597" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="B598" t="s">
         <v>4</v>
       </c>
       <c r="C598" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="B599" t="s">
         <v>4</v>
       </c>
       <c r="C599" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="B600" t="s">
         <v>4</v>
       </c>
       <c r="C600" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="B601" t="s">
         <v>4</v>
       </c>
       <c r="C601" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="602">
@@ -11642,21 +11654,21 @@
         <v>387</v>
       </c>
       <c r="B602" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C602" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="B603" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C603" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="604">
@@ -11664,10 +11676,10 @@
         <v>8</v>
       </c>
       <c r="B604" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C604" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="605">
@@ -11675,10 +11687,10 @@
         <v>60</v>
       </c>
       <c r="B605" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C605" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="606">
@@ -11686,10 +11698,10 @@
         <v>78</v>
       </c>
       <c r="B606" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C606" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="607">
@@ -11697,10 +11709,10 @@
         <v>114</v>
       </c>
       <c r="B607" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C607" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="608">
@@ -11708,32 +11720,32 @@
         <v>118</v>
       </c>
       <c r="B608" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C608" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="B609" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C609" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="B610" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C610" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="611">
@@ -11741,10 +11753,10 @@
         <v>142</v>
       </c>
       <c r="B611" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C611" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="612">
@@ -11752,21 +11764,21 @@
         <v>152</v>
       </c>
       <c r="B612" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C612" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="B613" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C613" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="614">
@@ -11774,10 +11786,10 @@
         <v>154</v>
       </c>
       <c r="B614" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C614" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="615">
@@ -11785,10 +11797,10 @@
         <v>156</v>
       </c>
       <c r="B615" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C615" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="616">
@@ -11796,10 +11808,10 @@
         <v>158</v>
       </c>
       <c r="B616" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C616" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="617">
@@ -11807,10 +11819,10 @@
         <v>182</v>
       </c>
       <c r="B617" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C617" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="618">
@@ -11818,10 +11830,10 @@
         <v>327</v>
       </c>
       <c r="B618" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C618" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="619">
@@ -11829,32 +11841,32 @@
         <v>339</v>
       </c>
       <c r="B619" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C619" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="B620" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C620" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="B621" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C621" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="622">
@@ -11862,10 +11874,10 @@
         <v>353</v>
       </c>
       <c r="B622" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C622" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="623">
@@ -11873,10 +11885,10 @@
         <v>355</v>
       </c>
       <c r="B623" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C623" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="624">
@@ -11884,10 +11896,10 @@
         <v>357</v>
       </c>
       <c r="B624" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C624" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="625">
@@ -11895,10 +11907,10 @@
         <v>359</v>
       </c>
       <c r="B625" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C625" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="626">
@@ -11906,10 +11918,10 @@
         <v>371</v>
       </c>
       <c r="B626" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C626" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="627">
@@ -11917,10 +11929,10 @@
         <v>381</v>
       </c>
       <c r="B627" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C627" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="628">
@@ -11928,10 +11940,10 @@
         <v>395</v>
       </c>
       <c r="B628" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C628" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="629">
@@ -11939,10 +11951,10 @@
         <v>431</v>
       </c>
       <c r="B629" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C629" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="630">
@@ -11950,10 +11962,10 @@
         <v>471</v>
       </c>
       <c r="B630" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C630" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="631">
@@ -11961,21 +11973,21 @@
         <v>473</v>
       </c>
       <c r="B631" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C631" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="B632" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C632" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="633">
@@ -11983,10 +11995,10 @@
         <v>497</v>
       </c>
       <c r="B633" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C633" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="634">
@@ -11994,10 +12006,10 @@
         <v>511</v>
       </c>
       <c r="B634" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C634" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="635">
@@ -12005,10 +12017,10 @@
         <v>529</v>
       </c>
       <c r="B635" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C635" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="636">
@@ -12016,10 +12028,10 @@
         <v>531</v>
       </c>
       <c r="B636" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C636" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="637">
@@ -12027,10 +12039,10 @@
         <v>539</v>
       </c>
       <c r="B637" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C637" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="638">
@@ -12038,10 +12050,10 @@
         <v>545</v>
       </c>
       <c r="B638" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C638" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="639">
@@ -12049,10 +12061,10 @@
         <v>563</v>
       </c>
       <c r="B639" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C639" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="640">
@@ -12060,10 +12072,10 @@
         <v>565</v>
       </c>
       <c r="B640" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C640" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="641">
@@ -12071,10 +12083,10 @@
         <v>567</v>
       </c>
       <c r="B641" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C641" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="642">
@@ -12082,10 +12094,10 @@
         <v>579</v>
       </c>
       <c r="B642" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C642" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="643">
@@ -12093,10 +12105,10 @@
         <v>583</v>
       </c>
       <c r="B643" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C643" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="644">
@@ -12104,10 +12116,10 @@
         <v>587</v>
       </c>
       <c r="B644" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C644" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="645">
@@ -12115,10 +12127,10 @@
         <v>585</v>
       </c>
       <c r="B645" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C645" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="646">
@@ -12126,10 +12138,10 @@
         <v>589</v>
       </c>
       <c r="B646" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C646" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="647">
@@ -12137,10 +12149,10 @@
         <v>575</v>
       </c>
       <c r="B647" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C647" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="648">
@@ -12148,10 +12160,10 @@
         <v>591</v>
       </c>
       <c r="B648" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C648" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="649">
@@ -12159,10 +12171,10 @@
         <v>593</v>
       </c>
       <c r="B649" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C649" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="650">
@@ -12170,10 +12182,10 @@
         <v>615</v>
       </c>
       <c r="B650" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C650" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="651">
@@ -12181,10 +12193,10 @@
         <v>607</v>
       </c>
       <c r="B651" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C651" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="652">
@@ -12192,10 +12204,10 @@
         <v>621</v>
       </c>
       <c r="B652" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C652" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="653">
@@ -12203,10 +12215,10 @@
         <v>633</v>
       </c>
       <c r="B653" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C653" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="654">
@@ -12214,10 +12226,10 @@
         <v>631</v>
       </c>
       <c r="B654" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C654" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="655">
@@ -12225,10 +12237,10 @@
         <v>639</v>
       </c>
       <c r="B655" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C655" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="656">
@@ -12236,10 +12248,10 @@
         <v>627</v>
       </c>
       <c r="B656" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C656" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="657">
@@ -12247,10 +12259,10 @@
         <v>653</v>
       </c>
       <c r="B657" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C657" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="658">
@@ -12258,10 +12270,10 @@
         <v>667</v>
       </c>
       <c r="B658" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C658" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="659">
@@ -12269,10 +12281,10 @@
         <v>683</v>
       </c>
       <c r="B659" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C659" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="660">
@@ -12280,10 +12292,10 @@
         <v>691</v>
       </c>
       <c r="B660" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C660" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="661">
@@ -12291,10 +12303,10 @@
         <v>711</v>
       </c>
       <c r="B661" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C661" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="662">
@@ -12302,10 +12314,10 @@
         <v>715</v>
       </c>
       <c r="B662" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C662" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="663">
@@ -12313,10 +12325,10 @@
         <v>719</v>
       </c>
       <c r="B663" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C663" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="664">
@@ -12324,10 +12336,10 @@
         <v>723</v>
       </c>
       <c r="B664" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C664" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="665">
@@ -12335,10 +12347,10 @@
         <v>727</v>
       </c>
       <c r="B665" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C665" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="666">
@@ -12346,10 +12358,10 @@
         <v>729</v>
       </c>
       <c r="B666" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C666" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="667">
@@ -12357,10 +12369,10 @@
         <v>739</v>
       </c>
       <c r="B667" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C667" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="668">
@@ -12368,10 +12380,10 @@
         <v>763</v>
       </c>
       <c r="B668" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C668" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="669">
@@ -12379,10 +12391,10 @@
         <v>775</v>
       </c>
       <c r="B669" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C669" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="670">
@@ -12390,10 +12402,10 @@
         <v>777</v>
       </c>
       <c r="B670" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C670" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="671">
@@ -12401,10 +12413,10 @@
         <v>781</v>
       </c>
       <c r="B671" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C671" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="672">
@@ -12412,10 +12424,10 @@
         <v>787</v>
       </c>
       <c r="B672" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C672" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="673">
@@ -12423,10 +12435,10 @@
         <v>791</v>
       </c>
       <c r="B673" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C673" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="674">
@@ -12434,10 +12446,10 @@
         <v>797</v>
       </c>
       <c r="B674" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C674" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="675">
@@ -12445,10 +12457,10 @@
         <v>803</v>
       </c>
       <c r="B675" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C675" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="676">
@@ -12456,10 +12468,10 @@
         <v>809</v>
       </c>
       <c r="B676" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C676" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="677">
@@ -12467,10 +12479,10 @@
         <v>823</v>
       </c>
       <c r="B677" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C677" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="678">
@@ -12478,10 +12490,10 @@
         <v>829</v>
       </c>
       <c r="B678" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C678" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="679">
@@ -12489,10 +12501,10 @@
         <v>845</v>
       </c>
       <c r="B679" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C679" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="680">
@@ -12500,10 +12512,10 @@
         <v>849</v>
       </c>
       <c r="B680" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C680" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="681">
@@ -12511,10 +12523,10 @@
         <v>857</v>
       </c>
       <c r="B681" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C681" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="682">
@@ -12522,10 +12534,10 @@
         <v>867</v>
       </c>
       <c r="B682" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C682" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="683">
@@ -12533,10 +12545,10 @@
         <v>883</v>
       </c>
       <c r="B683" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C683" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="684">
@@ -12544,10 +12556,10 @@
         <v>885</v>
       </c>
       <c r="B684" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C684" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="685">
@@ -12555,10 +12567,10 @@
         <v>909</v>
       </c>
       <c r="B685" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C685" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="686">
@@ -12566,10 +12578,10 @@
         <v>965</v>
       </c>
       <c r="B686" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C686" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="687">
@@ -12577,10 +12589,10 @@
         <v>971</v>
       </c>
       <c r="B687" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C687" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="688">
@@ -12588,10 +12600,10 @@
         <v>983</v>
       </c>
       <c r="B688" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C688" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="689">
@@ -12599,10 +12611,10 @@
         <v>1003</v>
       </c>
       <c r="B689" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C689" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="690">
@@ -12610,21 +12622,21 @@
         <v>1005</v>
       </c>
       <c r="B690" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C690" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="B691" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C691" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="692">
@@ -12632,263 +12644,263 @@
         <v>1023</v>
       </c>
       <c r="B692" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C692" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="B693" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C693" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B694" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C694" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B695" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C695" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B696" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C696" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B697" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C697" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B698" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C698" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B699" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C699" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B700" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C700" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B701" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C701" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B702" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C702" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="B703" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C703" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="B704" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C704" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="B705" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C705" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B706" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C706" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B707" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C707" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="B708" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C708" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="B709" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C709" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="B710" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C710" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="B711" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C711" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="B712" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C712" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="B713" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C713" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="B714" t="s">
         <v>4</v>
       </c>
       <c r="C714" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="B715" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C715" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="716">
@@ -12896,10 +12908,10 @@
         <v>58</v>
       </c>
       <c r="B716" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C716" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="717">
@@ -12907,10 +12919,10 @@
         <v>64</v>
       </c>
       <c r="B717" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C717" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="718">
@@ -12918,10 +12930,10 @@
         <v>66</v>
       </c>
       <c r="B718" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C718" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="719">
@@ -12929,32 +12941,32 @@
         <v>60</v>
       </c>
       <c r="B719" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C719" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="B720" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C720" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="B721" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C721" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="722">
@@ -12962,10 +12974,10 @@
         <v>72</v>
       </c>
       <c r="B722" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C722" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="723">
@@ -12973,10 +12985,10 @@
         <v>84</v>
       </c>
       <c r="B723" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C723" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="724">
@@ -12984,10 +12996,10 @@
         <v>86</v>
       </c>
       <c r="B724" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C724" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="725">
@@ -12995,10 +13007,10 @@
         <v>114</v>
       </c>
       <c r="B725" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C725" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="726">
@@ -13006,10 +13018,10 @@
         <v>118</v>
       </c>
       <c r="B726" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C726" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="727">
@@ -13017,10 +13029,10 @@
         <v>126</v>
       </c>
       <c r="B727" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C727" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="728">
@@ -13028,21 +13040,21 @@
         <v>134</v>
       </c>
       <c r="B728" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C728" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="B729" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C729" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="730">
@@ -13050,10 +13062,10 @@
         <v>158</v>
       </c>
       <c r="B730" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C730" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="731">
@@ -13061,10 +13073,10 @@
         <v>168</v>
       </c>
       <c r="B731" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C731" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="732">
@@ -13072,43 +13084,43 @@
         <v>196</v>
       </c>
       <c r="B732" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C732" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="B733" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C733" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="B734" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C734" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="B735" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C735" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="736">
@@ -13116,43 +13128,43 @@
         <v>208</v>
       </c>
       <c r="B736" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C736" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="B737" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C737" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="B738" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C738" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="B739" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C739" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="740">
@@ -13160,43 +13172,43 @@
         <v>220</v>
       </c>
       <c r="B740" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C740" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B741" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C741" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="B742" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C742" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="B743" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C743" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="744">
@@ -13204,43 +13216,43 @@
         <v>232</v>
       </c>
       <c r="B744" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C744" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="B745" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C745" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="B746" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C746" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="B747" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C747" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="748">
@@ -13248,43 +13260,43 @@
         <v>258</v>
       </c>
       <c r="B748" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C748" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="B749" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C749" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="B750" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C750" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="B751" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C751" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="752">
@@ -13292,32 +13304,32 @@
         <v>287</v>
       </c>
       <c r="B752" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C752" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="B753" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C753" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="B754" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C754" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="755">
@@ -13325,43 +13337,43 @@
         <v>297</v>
       </c>
       <c r="B755" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C755" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="B756" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C756" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="B757" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C757" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="B758" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C758" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="759">
@@ -13369,43 +13381,43 @@
         <v>309</v>
       </c>
       <c r="B759" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C759" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="B760" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C760" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="B761" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C761" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="B762" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C762" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="763">
@@ -13413,10 +13425,10 @@
         <v>317</v>
       </c>
       <c r="B763" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C763" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="764">
@@ -13424,10 +13436,10 @@
         <v>323</v>
       </c>
       <c r="B764" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C764" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="765">
@@ -13435,10 +13447,10 @@
         <v>335</v>
       </c>
       <c r="B765" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C765" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="766">
@@ -13446,10 +13458,10 @@
         <v>371</v>
       </c>
       <c r="B766" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C766" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="767">
@@ -13457,21 +13469,21 @@
         <v>373</v>
       </c>
       <c r="B767" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C767" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="B768" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C768" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="769">
@@ -13479,10 +13491,10 @@
         <v>377</v>
       </c>
       <c r="B769" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C769" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="770">
@@ -13490,10 +13502,10 @@
         <v>381</v>
       </c>
       <c r="B770" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C770" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="771">
@@ -13501,32 +13513,32 @@
         <v>383</v>
       </c>
       <c r="B771" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C771" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="B772" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C772" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="B773" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C773" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="774">
@@ -13534,10 +13546,10 @@
         <v>441</v>
       </c>
       <c r="B774" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C774" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="775">
@@ -13545,10 +13557,10 @@
         <v>461</v>
       </c>
       <c r="B775" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C775" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="776">
@@ -13556,10 +13568,10 @@
         <v>475</v>
       </c>
       <c r="B776" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C776" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="777">
@@ -13567,21 +13579,21 @@
         <v>511</v>
       </c>
       <c r="B777" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C777" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="B778" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C778" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="779">
@@ -13589,10 +13601,10 @@
         <v>515</v>
       </c>
       <c r="B779" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C779" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="780">
@@ -13600,32 +13612,32 @@
         <v>517</v>
       </c>
       <c r="B780" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C780" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="B781" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C781" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="B782" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C782" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="783">
@@ -13633,21 +13645,21 @@
         <v>529</v>
       </c>
       <c r="B783" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C783" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="B784" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C784" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="785">
@@ -13655,10 +13667,10 @@
         <v>531</v>
       </c>
       <c r="B785" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C785" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="786">
@@ -13666,10 +13678,10 @@
         <v>543</v>
       </c>
       <c r="B786" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C786" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="787">
@@ -13677,10 +13689,10 @@
         <v>545</v>
       </c>
       <c r="B787" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C787" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="788">
@@ -13688,10 +13700,10 @@
         <v>577</v>
       </c>
       <c r="B788" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C788" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="789">
@@ -13699,10 +13711,10 @@
         <v>591</v>
       </c>
       <c r="B789" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C789" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="790">
@@ -13710,10 +13722,10 @@
         <v>601</v>
       </c>
       <c r="B790" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C790" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="791">
@@ -13721,10 +13733,10 @@
         <v>593</v>
       </c>
       <c r="B791" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C791" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="792">
@@ -13732,10 +13744,10 @@
         <v>605</v>
       </c>
       <c r="B792" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C792" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="793">
@@ -13743,21 +13755,21 @@
         <v>607</v>
       </c>
       <c r="B793" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C793" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="B794" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C794" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="795">
@@ -13765,10 +13777,10 @@
         <v>633</v>
       </c>
       <c r="B795" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C795" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="796">
@@ -13776,10 +13788,10 @@
         <v>631</v>
       </c>
       <c r="B796" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C796" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="797">
@@ -13787,10 +13799,10 @@
         <v>641</v>
       </c>
       <c r="B797" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C797" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="798">
@@ -13798,32 +13810,32 @@
         <v>649</v>
       </c>
       <c r="B798" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C798" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B799" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C799" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="B800" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C800" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="801">
@@ -13831,10 +13843,10 @@
         <v>661</v>
       </c>
       <c r="B801" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C801" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="802">
@@ -13842,10 +13854,10 @@
         <v>627</v>
       </c>
       <c r="B802" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C802" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="803">
@@ -13853,21 +13865,21 @@
         <v>671</v>
       </c>
       <c r="B803" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C803" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="B804" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C804" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="805">
@@ -13875,10 +13887,10 @@
         <v>683</v>
       </c>
       <c r="B805" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C805" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="806">
@@ -13886,10 +13898,10 @@
         <v>691</v>
       </c>
       <c r="B806" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C806" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="807">
@@ -13897,10 +13909,10 @@
         <v>707</v>
       </c>
       <c r="B807" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C807" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="808">
@@ -13908,10 +13920,10 @@
         <v>715</v>
       </c>
       <c r="B808" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C808" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="809">
@@ -13919,10 +13931,10 @@
         <v>717</v>
       </c>
       <c r="B809" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C809" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="810">
@@ -13930,10 +13942,10 @@
         <v>719</v>
       </c>
       <c r="B810" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C810" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="811">
@@ -13941,21 +13953,21 @@
         <v>729</v>
       </c>
       <c r="B811" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C811" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="B812" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C812" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="813">
@@ -13963,21 +13975,21 @@
         <v>745</v>
       </c>
       <c r="B813" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C813" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="B814" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C814" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="815">
@@ -13985,21 +13997,21 @@
         <v>781</v>
       </c>
       <c r="B815" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C815" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="B816" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C816" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="817">
@@ -14007,10 +14019,10 @@
         <v>807</v>
       </c>
       <c r="B817" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C817" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="818">
@@ -14018,10 +14030,10 @@
         <v>811</v>
       </c>
       <c r="B818" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C818" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="819">
@@ -14029,10 +14041,10 @@
         <v>833</v>
       </c>
       <c r="B819" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C819" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="820">
@@ -14040,10 +14052,10 @@
         <v>835</v>
       </c>
       <c r="B820" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C820" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="821">
@@ -14051,10 +14063,10 @@
         <v>853</v>
       </c>
       <c r="B821" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C821" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="822">
@@ -14062,10 +14074,10 @@
         <v>851</v>
       </c>
       <c r="B822" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C822" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="823">
@@ -14073,54 +14085,54 @@
         <v>855</v>
       </c>
       <c r="B823" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C823" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="B824" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C824" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="B825" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C825" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="B826" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C826" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="B827" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C827" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="828">
@@ -14128,10 +14140,10 @@
         <v>849</v>
       </c>
       <c r="B828" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C828" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="829">
@@ -14139,10 +14151,10 @@
         <v>867</v>
       </c>
       <c r="B829" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C829" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="830">
@@ -14150,10 +14162,10 @@
         <v>871</v>
       </c>
       <c r="B830" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C830" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="831">
@@ -14161,21 +14173,21 @@
         <v>873</v>
       </c>
       <c r="B831" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C831" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="B832" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C832" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="833">
@@ -14183,10 +14195,10 @@
         <v>883</v>
       </c>
       <c r="B833" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C833" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="834">
@@ -14194,10 +14206,10 @@
         <v>885</v>
       </c>
       <c r="B834" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C834" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="835">
@@ -14205,10 +14217,10 @@
         <v>893</v>
       </c>
       <c r="B835" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C835" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="836">
@@ -14216,10 +14228,10 @@
         <v>895</v>
       </c>
       <c r="B836" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C836" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="837">
@@ -14227,10 +14239,10 @@
         <v>901</v>
       </c>
       <c r="B837" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C837" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="838">
@@ -14238,10 +14250,10 @@
         <v>903</v>
       </c>
       <c r="B838" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C838" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="839">
@@ -14249,10 +14261,10 @@
         <v>905</v>
       </c>
       <c r="B839" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C839" t="s">
-        <v>1416</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="840">
@@ -14260,10 +14272,10 @@
         <v>913</v>
       </c>
       <c r="B840" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C840" t="s">
-        <v>1494</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="841">
@@ -14271,10 +14283,10 @@
         <v>915</v>
       </c>
       <c r="B841" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C841" t="s">
-        <v>1495</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="842">
@@ -14282,10 +14294,10 @@
         <v>925</v>
       </c>
       <c r="B842" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C842" t="s">
-        <v>1496</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="843">
@@ -14293,10 +14305,10 @@
         <v>947</v>
       </c>
       <c r="B843" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C843" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="844">
@@ -14304,21 +14316,21 @@
         <v>961</v>
       </c>
       <c r="B844" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C844" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
       <c r="B845" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C845" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="846">
@@ -14326,10 +14338,10 @@
         <v>965</v>
       </c>
       <c r="B846" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C846" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="847">
@@ -14337,10 +14349,10 @@
         <v>969</v>
       </c>
       <c r="B847" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C847" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="848">
@@ -14348,21 +14360,21 @@
         <v>973</v>
       </c>
       <c r="B848" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C848" t="s">
-        <v>1503</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="s">
-        <v>1504</v>
+        <v>1507</v>
       </c>
       <c r="B849" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C849" t="s">
-        <v>1505</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="850">
@@ -14370,10 +14382,10 @@
         <v>983</v>
       </c>
       <c r="B850" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C850" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="851">
@@ -14381,10 +14393,10 @@
         <v>999</v>
       </c>
       <c r="B851" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C851" t="s">
-        <v>1507</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="852">
@@ -14392,10 +14404,10 @@
         <v>1005</v>
       </c>
       <c r="B852" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C852" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="853">
@@ -14403,10 +14415,10 @@
         <v>1015</v>
       </c>
       <c r="B853" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C853" t="s">
-        <v>1509</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="854">
@@ -14414,10 +14426,10 @@
         <v>1019</v>
       </c>
       <c r="B854" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C854" t="s">
-        <v>1510</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="855">
@@ -14425,32 +14437,32 @@
         <v>1023</v>
       </c>
       <c r="B855" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C855" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="B856" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C856" t="s">
-        <v>1513</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="s">
-        <v>1514</v>
+        <v>1517</v>
       </c>
       <c r="B857" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C857" t="s">
-        <v>1515</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="858">
@@ -14458,153 +14470,153 @@
         <v>1031</v>
       </c>
       <c r="B858" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C858" t="s">
-        <v>1516</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B859" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C859" t="s">
-        <v>1517</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B860" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C860" t="s">
-        <v>1518</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B861" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C861" t="s">
-        <v>1519</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B862" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C862" t="s">
-        <v>1520</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B863" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C863" t="s">
-        <v>1521</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="s">
-        <v>1522</v>
+        <v>1525</v>
       </c>
       <c r="B864" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C864" t="s">
-        <v>1523</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B865" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C865" t="s">
-        <v>1524</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="B866" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C866" t="s">
-        <v>1525</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="B867" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C867" t="s">
-        <v>1526</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="B868" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C868" t="s">
-        <v>1527</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="B869" t="s">
         <v>635</v>
       </c>
       <c r="C869" t="s">
-        <v>1528</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="s">
-        <v>1529</v>
+        <v>1532</v>
       </c>
       <c r="B870" t="s">
         <v>635</v>
       </c>
       <c r="C870" t="s">
-        <v>1530</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="s">
-        <v>1531</v>
+        <v>1534</v>
       </c>
       <c r="B871" t="s">
         <v>635</v>
       </c>
       <c r="C871" t="s">
-        <v>1532</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="872">
@@ -14615,7 +14627,7 @@
         <v>635</v>
       </c>
       <c r="C872" t="s">
-        <v>1533</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="873">
@@ -14626,7 +14638,7 @@
         <v>635</v>
       </c>
       <c r="C873" t="s">
-        <v>1534</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="874">
@@ -14637,7 +14649,7 @@
         <v>635</v>
       </c>
       <c r="C874" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="875">
@@ -14648,7 +14660,7 @@
         <v>635</v>
       </c>
       <c r="C875" t="s">
-        <v>1536</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="876">
@@ -14659,18 +14671,18 @@
         <v>635</v>
       </c>
       <c r="C876" t="s">
-        <v>1537</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="s">
-        <v>1538</v>
+        <v>1541</v>
       </c>
       <c r="B877" t="s">
         <v>635</v>
       </c>
       <c r="C877" t="s">
-        <v>1539</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="878">
@@ -14681,7 +14693,7 @@
         <v>635</v>
       </c>
       <c r="C878" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="879">
@@ -14692,7 +14704,7 @@
         <v>635</v>
       </c>
       <c r="C879" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="880">
@@ -14703,7 +14715,7 @@
         <v>635</v>
       </c>
       <c r="C880" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="881">
@@ -14714,7 +14726,7 @@
         <v>635</v>
       </c>
       <c r="C881" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="882">
@@ -14725,7 +14737,7 @@
         <v>635</v>
       </c>
       <c r="C882" t="s">
-        <v>1544</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="883">
@@ -14736,7 +14748,7 @@
         <v>635</v>
       </c>
       <c r="C883" t="s">
-        <v>1545</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="884">
@@ -14747,7 +14759,7 @@
         <v>635</v>
       </c>
       <c r="C884" t="s">
-        <v>1546</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="885">
@@ -14758,7 +14770,7 @@
         <v>635</v>
       </c>
       <c r="C885" t="s">
-        <v>1547</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="886">
@@ -14769,7 +14781,7 @@
         <v>635</v>
       </c>
       <c r="C886" t="s">
-        <v>1548</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="887">
@@ -14780,7 +14792,7 @@
         <v>635</v>
       </c>
       <c r="C887" t="s">
-        <v>1549</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="888">
@@ -14791,95 +14803,95 @@
         <v>635</v>
       </c>
       <c r="C888" t="s">
-        <v>1550</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B889" t="s">
         <v>635</v>
       </c>
       <c r="C889" t="s">
-        <v>1551</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="B890" t="s">
         <v>635</v>
       </c>
       <c r="C890" t="s">
-        <v>1539</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="B891" t="s">
         <v>635</v>
       </c>
       <c r="C891" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="B892" t="s">
         <v>635</v>
       </c>
       <c r="C892" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
       <c r="B893" t="s">
         <v>4</v>
       </c>
       <c r="C893" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
       <c r="B894" t="s">
         <v>4</v>
       </c>
       <c r="C894" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="B895" t="s">
         <v>4</v>
       </c>
       <c r="C895" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
       <c r="B896" t="s">
         <v>4</v>
       </c>
       <c r="C896" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
     </row>
   </sheetData>
